--- a/AAII_Financials/Quarterly/ORI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="92">
   <si>
     <t>ORI</t>
   </si>
@@ -656,344 +656,351 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2503800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2399400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2389200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2424300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2208500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2114000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2002100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2341500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1871700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2015900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1941100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1760100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1798100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1758500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1967100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2071800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2180800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2126800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2257600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2211500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2133800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1987500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2236800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1872500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1673000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1726700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2018100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1713700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1618400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1513000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1592400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1651300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1589400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1482400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1726200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1593000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1499000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1444800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1548800</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1496000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>896700</v>
+      </c>
+      <c r="E9" s="3">
         <v>840100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>912100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>856800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>830600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>777600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>792900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>815900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>741500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>697400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>711400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>663300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>617700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>603800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1069,53 +1076,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1607100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1559300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1477100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1567500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1377900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1336400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1209200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1525600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1130200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1318500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1229700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1096800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1180400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1154700</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1191,8 +1201,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1511,12 +1531,12 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>10700</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1529,8 +1549,8 @@
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1613,7 +1636,7 @@
         <v>8900</v>
       </c>
       <c r="F15" s="3">
-        <v>9800</v>
+        <v>8900</v>
       </c>
       <c r="G15" s="3">
         <v>9800</v>
@@ -1625,7 +1648,7 @@
         <v>9800</v>
       </c>
       <c r="J15" s="3">
-        <v>8300</v>
+        <v>9800</v>
       </c>
       <c r="K15" s="3">
         <v>8300</v>
@@ -1637,7 +1660,7 @@
         <v>8300</v>
       </c>
       <c r="N15" s="3">
-        <v>7100</v>
+        <v>8300</v>
       </c>
       <c r="O15" s="3">
         <v>7100</v>
@@ -1646,7 +1669,7 @@
         <v>7100</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2066900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1968100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2108800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2053800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1930500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1788300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1854100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1893300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1736000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1600700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1676400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1679600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1580600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1492400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1679700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1824300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1848200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1807000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1914600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1889400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1845500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1713800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1946000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1635200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1517200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1522100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1823100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1508700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1428700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1339400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1410600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1434500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1373900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1321900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1356700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1517400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1336400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1263500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1341800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1319100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>436900</v>
+      </c>
+      <c r="E18" s="3">
         <v>431300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>280400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>370500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>278000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>325700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>148000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>448200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>135700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>415200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>264700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>80500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>217500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>266100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>287400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>247500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>332600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>319800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>343000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>322100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>288300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>273700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>290800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>237300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>155800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>204600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>195000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>205000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>189700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>173600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>181800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>216800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>215500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>160500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>369500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>75600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>162600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>181300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>207000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>176900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,175 +2085,179 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>378500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-350800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-370600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>79700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>463000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-199300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>119800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>367500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>373400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>79100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>353700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-962600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>160300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>57100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>26100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>355500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-311500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>128200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>41100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-152100</v>
       </c>
-      <c r="AK20" s="3">
-        <v>0</v>
-      </c>
       <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
         <v>-300</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-400</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-200</v>
       </c>
-      <c r="AO20" s="3">
-        <v>0</v>
-      </c>
       <c r="AP20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>445400</v>
+      </c>
+      <c r="E21" s="3">
         <v>439900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>289700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>379800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>287400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>335300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>160200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>456400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>143800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>423200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>269600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>87400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>224700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>273100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>5</v>
       </c>
@@ -2296,374 +2333,386 @@
       <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ21" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E22" s="3">
         <v>17700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>21300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>14400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>14700</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>15800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>16000</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>16400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>16200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>12600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>410000</v>
+      </c>
+      <c r="E23" s="3">
         <v>413300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>263200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>352700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>260000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>307700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>130600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>426800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>113300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>398500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>237400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>63900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>196900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>249100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>649100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-119600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>382600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>789500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>106000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>396000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>630600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>652300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>306900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>499100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-769900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>346100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>252400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>205400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>518500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-137600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>335100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>246600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-6000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>354800</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>59500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>146200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>164700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>190800</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>164000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>85700</v>
+      </c>
+      <c r="E24" s="3">
         <v>83800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>55900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>72700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>51700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>61600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>87900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>21500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>81800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>11300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>49300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>136900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-27800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-14400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>76300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>162500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>79500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>128500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>132400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>60900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>101400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-165100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>70300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>39900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>106200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-31100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>59800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>48800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-10100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-8000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>13400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>44600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>51600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>58800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>324300</v>
+      </c>
+      <c r="E26" s="3">
         <v>329500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>207300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>280000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>208300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>246100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>105100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>338900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>91800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>316700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>190600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>52600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>155500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>199800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>512200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-91800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-40200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>306300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>627000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>88800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>316500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>502100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>519900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>246000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>397700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-604800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>275800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>202900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>165500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>412300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-106500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>275300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>197800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>362800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>46100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>101600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>113100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>132000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>322300</v>
+      </c>
+      <c r="E27" s="3">
         <v>330000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>206400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>279500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>204400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>245000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>105100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>338900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>91800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>316700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>190600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>52600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>155500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>199800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>512100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-91600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-40000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>306300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>627100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>88600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>316300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>502100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>519700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>246000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>397700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-604600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>275800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>202800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>165500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>412200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-106500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>275200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>362700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>46100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>101600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>113100</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>131900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-63100</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-378500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>350800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>370600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-79700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-463000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>199300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-119800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-367500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-373400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-79100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-353700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>962600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-160300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-57100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-26100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-355500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>311500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-128200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-41100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>152100</v>
       </c>
-      <c r="AK32" s="3">
-        <v>0</v>
-      </c>
       <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
         <v>300</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>400</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>200</v>
       </c>
-      <c r="AO32" s="3">
-        <v>0</v>
-      </c>
       <c r="AP32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ32" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>322300</v>
+      </c>
+      <c r="E33" s="3">
         <v>330000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>206400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>279500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>204400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>245000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>105100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>338900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>91800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>316700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>190600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>52600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>155500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>199800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>512100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-91600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-40000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>306300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>627100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>88600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>316300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>502100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>519700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>246000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>397700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-604600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>275800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>202800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>165500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>412200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-106500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>275200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>299600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>46100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>101600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>113100</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>131900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>322300</v>
+      </c>
+      <c r="E35" s="3">
         <v>330000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>206400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>279500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>204400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>245000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>105100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>338900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>91800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>316700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>190600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>52600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>155500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>199800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>512100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-91600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-40000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>306300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>627100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>88600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>316300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>502100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>519700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>246000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>397700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-604600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>275800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>202800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>165500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>412200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-106500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>275200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>299600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>46100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>101600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>113100</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>131900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,175 +4305,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>417700</v>
+      </c>
+      <c r="E41" s="3">
         <v>202100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>263200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>242500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>178100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>263700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>201900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>525200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>169200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>136900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>202800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>152100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>96300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>93700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>102400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>95100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>158100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>133400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>109200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>123400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>118700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>95000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>114000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>144500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>78800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>109600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>99800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>92800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>100300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>115200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>107900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>103400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>125900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>139200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>195100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>177200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>145700</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>144600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2233100</v>
+      </c>
+      <c r="E42" s="3">
         <v>1044900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1613600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1452500</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1215400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1036400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1403700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1317600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>1605100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>1338400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1032600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1146300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>853300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>863100</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4463,130 +4553,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3140200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2783300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2782200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2985100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2978300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2654700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2471600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2678600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2661400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2304300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2223200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2373300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2357200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2020300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1927500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2096900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2096000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1861800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1768700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1861400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1828700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1626600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1593900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1734000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1771900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1590300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1466700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1687500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1736100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1585000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1499400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1643000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1680200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1516100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1469700</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1589800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1605600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1461200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1390200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1508600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4629,8 +4725,8 @@
       <c r="P44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4707,53 +4803,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>703300</v>
+      </c>
+      <c r="E45" s="3">
         <v>757500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>755500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>723000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>712400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>691900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>736300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>817500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>847200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1044300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1031900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6987300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6435500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5991200</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4829,53 +4928,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6494300</v>
+      </c>
+      <c r="E46" s="3">
         <v>4787800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5414500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5403100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5084200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4646700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4813500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5338900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5282900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4823900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4490500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10659000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>9742300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>8968300</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4951,174 +5053,180 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>14858000</v>
+      </c>
+      <c r="E47" s="3">
         <v>15348500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>15225200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>15300500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14953900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14852100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>14675000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>15186300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14417800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>14986000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>14835000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>14266800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>14783300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15139100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15859900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15289100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>15864900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>16480300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>16576300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>16447100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>16348800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>15354100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>15330100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>14662900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>14240800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>13244800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>14359200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>13975400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>13888600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>13630500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>13023000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>13230100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>12897600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12850600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>13330800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>13349600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>12961700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>12917100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12775300</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>12652300</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
         <v>169300</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J48" s="3">
         <v>179700</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N48" s="3">
         <v>194400</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -5195,53 +5303,56 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>814800</v>
+      </c>
+      <c r="E49" s="3">
         <v>659100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>809400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>611600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>588500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>555700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>710900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>505300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>456500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>435800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>596100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>418700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>407400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>393300</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -5317,8 +5428,11 @@
       <c r="AP49" s="3">
         <v>0</v>
       </c>
+      <c r="AQ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,59 +5678,62 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>9425300</v>
+      </c>
+      <c r="E52" s="3">
         <v>8800600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8244300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8936800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8629100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7973600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7464000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>7813300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7368000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>6818600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>6385400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1047300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>917300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>897200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="R52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S52" s="3">
         <v>127400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5629,21 +5749,21 @@
       <c r="X52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
+      <c r="Y52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB52" s="3">
+      <c r="AA52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>130100</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD52" s="3" t="s">
         <v>5</v>
       </c>
@@ -5659,8 +5779,8 @@
       <c r="AH52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI52" s="3">
-        <v>0</v>
+      <c r="AI52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AJ52" s="3">
         <v>0</v>
@@ -5683,8 +5803,11 @@
       <c r="AP52" s="3">
         <v>0</v>
       </c>
+      <c r="AQ52" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31592400</v>
+      </c>
+      <c r="E54" s="3">
         <v>29596000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>29862700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>30252000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>29255700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28028100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27843100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28843800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27525200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27064300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>26501400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26400500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>25850300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>25397900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>25159400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>24947000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>25295400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25118800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24981800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>24989900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>24678400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23049300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22815200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>22248700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>21650300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20352200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>21076300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>21181800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20987700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20296900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19327100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19802300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19454200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18998800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>19403500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>19747400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>19357100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>18905400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>18591600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>18810600</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,53 +6145,54 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17016400</v>
+      </c>
+      <c r="E57" s="3">
         <v>16395600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5062500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16519900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15994300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15413600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15137500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15141000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14627600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14023300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13919100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14279100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13747000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13243500</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
@@ -6137,8 +6268,11 @@
       <c r="AP57" s="3">
         <v>0</v>
       </c>
+      <c r="AQ57" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -6146,11 +6280,11 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>52300</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6158,11 +6292,11 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>57900</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
@@ -6170,11 +6304,11 @@
         <v>0</v>
       </c>
       <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>58100</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
       <c r="O58" s="3">
         <v>0</v>
       </c>
@@ -6259,175 +6393,181 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4559000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4099500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3982500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4153400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4018500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3687100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3505400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3679100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3553600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3268500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3099500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3234300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3149000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2916700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16794500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>17071300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16724900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16055100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15617000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15919000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15591500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14976400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14657100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14648800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14237300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13778700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13627700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13869100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13630600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13184100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12910800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13205700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>13105700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12709600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12635400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13095800</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12794700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12445900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>12288200</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>12505100</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>22119800</v>
+      </c>
+      <c r="E60" s="3">
         <v>21048300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9699100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21225600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>20512400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>19587600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19248300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19329900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>18638400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>17787800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>17609600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17999900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17321600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>16663400</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6503,216 +6643,222 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2284000</v>
+      </c>
+      <c r="E61" s="3">
         <v>1590200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1730100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1589600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1589300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1589000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1734800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1988400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1987900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1987600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1753300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1590900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1590500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1590200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1597000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1596600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1594500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1594200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1588500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1588200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1590100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>947200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>966400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>966200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>968100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>967800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>974000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>973700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>975400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>975100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>981400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>981100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>974400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>974100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1448700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1526900</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1526100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1525500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1528700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1528000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>837900</v>
+      </c>
+      <c r="E62" s="3">
         <v>821600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>12285800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>771300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>759500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>733500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1112000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>866200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>784000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>794200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>622200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>894100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>771100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>735000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>40900</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
       <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
         <v>17200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>157200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>249500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>151500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>211100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>165000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>137300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>66400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>43700</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>5</v>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
@@ -6729,26 +6875,29 @@
       <c r="AJ62" s="3">
         <v>0</v>
       </c>
-      <c r="AK62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AL62" s="3">
+      <c r="AK62" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>71400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>79400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>64800</v>
       </c>
-      <c r="AO62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AP62" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ62" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>25504600</v>
+      </c>
+      <c r="E66" s="3">
         <v>23670700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>23934300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>23812900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>23052200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>22084600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22224200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>22398500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>21498600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>20663400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>20090700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>20484900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>19730500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>19066000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>18993200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>19268900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>18902300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>18368700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>18088600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>18660500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17899800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16597500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16628600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16174100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15791400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15209300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15076200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15387900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15093800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14631300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14180900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14491100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14350800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>13950200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>14670200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>15017400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>14695300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>14308800</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>14120000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>14364500</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5850500</v>
+      </c>
+      <c r="E72" s="3">
         <v>5652400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5515200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6037900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5853800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5721200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5519700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6135400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5912300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5889300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5644300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5520900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5536100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5450300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5319700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4874900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5341000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5450800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5214000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4653300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5082100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4831400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4394800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4234900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4051200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3715800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4386000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4170100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4326700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4220800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3849800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4014600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3797700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3658100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3206900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3323100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3326500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>3274300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3210600</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3127200</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6072800</v>
+      </c>
+      <c r="E76" s="3">
         <v>5911900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5914000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6422800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6185600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5917500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5618900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6445300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6026600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6400900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6410700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5915600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6119800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6331900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6166200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5678100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6393100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>6750100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>6893200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>6329400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>6778600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>6451800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>6186600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>6074600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>5858900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5142900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6000100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>5793900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5893900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5665600</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5146200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5311200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5103400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5048600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4733300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4730000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4661800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4596600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4471600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4446100</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>322300</v>
+      </c>
+      <c r="E81" s="3">
         <v>330000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>206400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>279500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>204400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>245000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>105100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>338900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>91800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>316700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>190600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>52600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>155500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>199800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>512100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-91600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-40000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>306300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>627100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>88600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>316300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>502100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>519700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>246000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>397700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-604600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>275800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>202800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>165500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>412200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-106500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>275200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>197700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>299600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>46100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>101600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>113100</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>131900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>110900</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,52 +8990,53 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E83" s="3">
+      <c r="E83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
         <v>39300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J83" s="3">
         <v>33000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N83" s="3">
         <v>28300</v>
       </c>
-      <c r="N83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>199700</v>
+      </c>
+      <c r="E89" s="3">
         <v>281400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>234900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>563900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>133800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>231700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>361700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>474800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>236500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>160400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>283400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>349800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>90600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>156600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>267300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>124800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>278400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>341100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>455000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>219400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>296100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>376200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>370600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>222000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>216200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>270200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>352700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>177300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>136100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>163400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>309700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>156600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>130800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-69400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>263300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>112700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>146100</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>235400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>238300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,8 +9910,9 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -9734,8 +9955,8 @@
       <c r="P91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R91" s="3">
         <v>0</v>
@@ -9812,8 +10033,11 @@
       <c r="AP91" s="3">
         <v>0</v>
       </c>
+      <c r="AQ91" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-537100</v>
+      </c>
+      <c r="E94" s="3">
         <v>518200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-83700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-381100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-140800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>428400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-45600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>114500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>282400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-355200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-114100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-110400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>200500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>49300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-60300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-49600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-285400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>188000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-384900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-827900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>88300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-293300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-325200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-190300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-36400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-246000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>16500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-114200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-110800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-247900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>178900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>96000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-271900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-45700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-72300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-186900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-760300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,76 +10455,77 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>76600</v>
+      </c>
+      <c r="E96" s="3">
         <v>693800</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G96" s="3">
         <v>70900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>73000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>567900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>64900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>66400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>69100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>71500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>66900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>67600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>69800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>71200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-67200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-373500</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-69600</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-69400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-517700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-66200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-65800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-369500</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-62400</v>
       </c>
       <c r="Z96" s="3">
         <v>-62400</v>
@@ -10300,52 +10534,55 @@
         <v>-62400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-62400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-62900</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-59900</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-359400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-59800</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-59600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-58300</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-58200</v>
       </c>
       <c r="AI96" s="3">
         <v>-58200</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-58200</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-324100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-50500</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-49500</v>
       </c>
       <c r="AM96" s="3">
         <v>-49500</v>
       </c>
       <c r="AN96" s="3">
+        <v>-49500</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-49300</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-48500</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-48600</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>553200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-860800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-130500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-118300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-78500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-598400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-639200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-233400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-482700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>128400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-117900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-183500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-288500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-193300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-228400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-478800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-69500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-56000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-504400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-46000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>594400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-379700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-59200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-64500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-62100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-114200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-359500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-56100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-62700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-67400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-54500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-92400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-332200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-39900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-47100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-49300</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-42200</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-47300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>497900</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>215800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-61200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>64500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-85500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>61700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-323100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>355900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>36200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-66400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>51400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>55900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>5700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-63000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>24700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>24100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-14100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>23700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>65600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-30600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>9700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>7300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-22500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-13300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-55700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>17700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>31600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1200</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-24100</v>
       </c>
     </row>
